--- a/光伏配储项目/电价数据/2026/琴韵站.xlsx
+++ b/光伏配储项目/电价数据/2026/琴韵站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.5535800000000001</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.3801</v>
+      </c>
+      <c r="C117" t="n">
+        <v>1.51442</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.85623</v>
+      </c>
+      <c r="E117" t="n">
+        <v>1.12447</v>
+      </c>
+      <c r="F117" t="n">
+        <v>1.01621</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.91289</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.71185</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.7214299999999999</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.44043</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.5355599999999999</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.58772</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.52115</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.68329</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.6834199999999999</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.67372</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.51444</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.70111</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.6914</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.6542899999999999</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.67984</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.5235599999999999</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.69421</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.3949</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.5432400000000001</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.6922699999999999</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.7001000000000001</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.54791</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.7251299999999999</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.81465</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.32406</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.34479</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30828</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.32773</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.33987</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.40192</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.85703</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.67601</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.6712</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.30557</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.45152</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.7329199999999999</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.75561</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.39779</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.37708</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>1.00851</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>0.99279</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>1.08369</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.75003</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>0.3196</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>0.697</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>0.50085</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.40634</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.40368</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.40831</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.7832</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.94851</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>1.31102</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>0.52275</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.75886</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.42558</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.76675</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.74675</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.9268500000000001</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.8935</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>1.04682</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>1.31373</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>1.12014</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>1.11743</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.7335499999999999</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>1.20858</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>1.16796</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>1.09637</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>1.22762</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>1.53419</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>1.10182</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>1.246</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>1.47533</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>1.30377</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>1.23513</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>1.79818</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>1.40945</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>1.35308</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>1.28371</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.8028</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.47923</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.4105</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.41268</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.42189</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.32993</v>
+      </c>
+      <c r="C118" t="n">
+        <v>1.16719</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E118" t="n">
+        <v>1.03671</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G118" t="n">
+        <v>1.1762</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.53624</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.5226499999999999</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.50627</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.51244</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.61112</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.51128</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.5854299999999999</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.49011</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.38091</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.39206</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.34051</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.48349</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.51861</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.50039</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.5106700000000001</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.51063</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.50039</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.50695</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.55569</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.76385</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>1.06768</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.83684</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.58877</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.48245</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.5354500000000001</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.45562</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.50705</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.9340900000000001</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>1.14993</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.7750199999999999</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>1.11933</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>1.03677</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>0.9855900000000001</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.70709</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.54761</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.5664199999999999</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.6789500000000001</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.35074</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>1.15223</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>1.22981</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>1.47366</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.30533</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>1.15688</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>1.62773</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>1.07795</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.8170499999999999</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>1.25015</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>1.13475</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>1.28266</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.31448</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.6214700000000001</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.6378400000000001</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.56989</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.6217200000000001</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>1.1592</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>1.16716</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>1.17585</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>1.17044</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.9672000000000001</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>1.1877</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>1.20251</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>1.19399</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>1.66862</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>1.16024</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>1.2055</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>1.20869</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>1.50494</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>1.40968</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>1.16654</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>1.50955</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>1.2639</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.7426799999999999</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.76485</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.91537</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.44058</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.43462</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.41311</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.33878</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.37719</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.35424</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33341</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32156</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.6011799999999999</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.6814</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.6914199999999999</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.53142</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.5754900000000001</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.5061</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.8314199999999999</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.5922200000000001</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.58424</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.55299</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.5549400000000001</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.6307200000000001</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.48402</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.57984</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.4861</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.36584</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.37083</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.35296</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.3583</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.34821</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.36268</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.35587</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.37972</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.39645</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.57347</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.5223</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.5547300000000001</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.49302</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.50971</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.49531</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.50547</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.45946</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.69226</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.83038</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>1.10748</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.8734700000000001</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.74402</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.70273</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.60424</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.30776</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.31738</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.3009</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.64295</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.42513</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.7285499999999999</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>1.1636</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>1.52043</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.6762899999999999</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>1.16589</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>1.6193</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>1.1874</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>1.1639</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.7922100000000001</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.9384</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>1.16269</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>1.16415</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.89161</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.5593400000000001</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.41354</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.47455</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.67402</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>1.16464</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>1.02754</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>1.16328</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>1.39112</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>1.23418</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>1.16463</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>1.2154</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>1.20925</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>1.39969</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>1.26791</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>1.28491</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>1.64765</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>1.16982</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>1.17276</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>1.78155</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>1.03788</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>1.07743</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>1.09829</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>1.08436</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>1.20322</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>1.16714</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>1.24706</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.99385</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.7536799999999999</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.71021</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.52986</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.41214</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.34314</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.31994</v>
+      </c>
+      <c r="C120" t="n">
+        <v>1.10792</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.71889</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.71225</v>
+      </c>
+      <c r="F120" t="n">
+        <v>1.1854</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.6773899999999999</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.85158</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.53815</v>
+      </c>
+      <c r="J120" t="n">
+        <v>1.58832</v>
+      </c>
+      <c r="K120" t="n">
+        <v>1.20566</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.58926</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.5213099999999999</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.6506799999999999</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.5820599999999999</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.5225299999999999</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.51413</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.50758</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.39917</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.45521</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.40824</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.33466</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.33321</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.32479</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.44224</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.34154</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.5063299999999999</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.51902</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.57347</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.49213</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.492</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.45727</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.48884</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.34568</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.6759400000000001</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.7180299999999999</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.93231</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>1.16668</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>1.30791</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.83704</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>1.5503</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>1.66556</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.90323</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.86349</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>1.16296</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>1.43942</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>1.77233</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.9519</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>1.20323</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0.68835</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>1.12252</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.52208</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.48493</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.65363</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.99498</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>1.1016</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>1.24839</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>1.16727</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>1.05962</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.98049</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>1.02531</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.98926</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>1.25006</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>1.4397</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.79226</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>1.34729</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>1.20421</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>1.18956</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.84687</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>1.07284</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>1.15987</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>1.12104</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>1.15264</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>1.2535</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>1.31706</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>1.15267</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>1.26834</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>1.18708</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>1.18579</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>1.186</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>1.18745</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>1.1877</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>1.17321</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>1.15079</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>1.17543</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.7231599999999999</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.52238</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.33491</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.72533</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.33196</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.33162</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.32861</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.33351</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.32161</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.74336</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.49335</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.40514</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.36471</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.34507</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.34029</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.33774</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.34887</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.32921</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.33089</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.33212</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.33098</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.32761</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.33113</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.33015</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.32682</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.3293</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.33365</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.32754</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.32585</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.32467</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.32365</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.32547</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.32514</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32909</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32821</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.33532</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.33111</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.3334</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.33772</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.47741</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.50427</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.5226799999999999</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.33543</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.33092</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.40001</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.31036</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.45509</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>0.33855</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>0.42553</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>0.45441</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>0.71593</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>0.84714</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>0.6143500000000001</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>0.70113</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>0.33958</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>0.7261599999999999</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>0.33205</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>0.8447</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>0.70462</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>0.33307</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>0.55032</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>0.54936</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>0.5381</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>0.5919</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>0.47024</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.08468000000000001</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.32334</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.30113</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.28039</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>0.26779</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>0.29601</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>0.3283</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>0.32995</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.5496599999999999</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.48179</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.5117</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.46618</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.63254</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.50182</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.48273</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.39923</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.48287</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.48704</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.59372</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.40247</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.5051100000000001</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.50557</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.40863</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.48577</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.35225</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.40806</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.39954</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.39844</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.40988</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.46754</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.38143</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.39643</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.40002</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.40474</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.35501</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35809</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.34469</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.35529</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.34388</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.368</v>
+      </c>
+      <c r="C122" t="n">
+        <v>1.18987</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.9647899999999999</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.98065</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.58992</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.6450900000000001</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.54192</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.52616</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.54075</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.36276</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.50942</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.50818</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.68013</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.5240499999999999</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.52435</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.50687</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.5077200000000001</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.34145</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.33941</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.50848</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.33687</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.33784</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.33688</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.33532</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.3388</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.35003</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.35201</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.34245</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.31602</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.26837</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.0733</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04659000000000001</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>0.30595</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04571</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04285</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04571</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04377</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04318</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>-0.04177</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>0.0453</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.27256</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.08278000000000001</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>-0.04341</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>0.29148</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>0.1286</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04295</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04502</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.0471</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.04699</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04486</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>0.0029</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.0423</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04677000000000001</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04593999999999999</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>-0.04233</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>0.30268</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04667</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04477</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04633</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04346</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>0.30012</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>0.30403</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>0.25266</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>0.26828</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>0.33599</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>0.27594</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>0.27915</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.35179</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.37971</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.42252</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.36121</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.36239</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.35586</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.35545</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.4458</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.5900599999999999</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.5356300000000001</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.35781</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.38903</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.38568</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.35983</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.38934</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.5577300000000001</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.53746</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.53667</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.35621</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.33995</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.36542</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.39522</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.36431</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.34551</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.3675</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.36598</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.33432</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.33127</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.55411</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.45741</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.4055299999999999</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.34404</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.32179</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.31673</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.32071</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.31274</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.31071</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.26972</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.308</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.30448</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.30894</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.30404</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.3039</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.30797</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.28515</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.28088</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17179</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.14841</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.16014</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15937</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23743</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.21479</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.29035</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.26772</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.30787</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.31032</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.32028</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.31786</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.31061</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.31392</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.31376</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.30012</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.32163</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32355</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.3283</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.33495</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.3847</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.74076</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.8733099999999999</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.67392</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.64789</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.6667999999999999</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.74779</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.93832</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.38749</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.36253</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.48055</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.7293099999999999</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.73094</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.8869</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.63014</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.53532</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.4824</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.44877</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.08512</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.29257</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.322</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.37711</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.29895</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.38048</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.7310800000000001</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.72737</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.63814</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.60249</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.4806</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.72807</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.7885700000000001</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.78239</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.78532</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.59997</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.7412300000000001</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>1.01755</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>1.40518</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.8423999999999999</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>1.43288</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>1.2958</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.7877799999999999</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>1.37964</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>1.04421</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.79954</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>1.39991</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.76444</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.4431</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.7738700000000001</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.80037</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.53035</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.78769</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.7850199999999999</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.87858</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.87879</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.50196</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.41209</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.41136</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.46008</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.21847</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87937</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55135</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.63937</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.54122</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.6137100000000001</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.5810700000000001</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.56113</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.5698099999999999</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.5764900000000001</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.5053</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.57804</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.55755</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.46669</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.49033</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.47799</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.38625</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.41494</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.43395</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.34402</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.53874</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.51048</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.5142</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.5107699999999999</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.5107200000000001</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.5467000000000001</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.51171</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.5636</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.46866</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.5665800000000001</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.49036</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.43726</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.59623</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.56363</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.6662</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>1.07974</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.6382100000000001</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.5024</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.56896</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>1.59876</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>1.00109</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>1.33886</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>1.30645</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>1.27484</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.5591699999999999</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.80179</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.57286</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.65064</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.5502899999999999</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.95511</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.77615</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.72527</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.64177</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.57505</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.98773</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.92784</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>1.78593</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.54118</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.66967</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.58693</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.66861</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.6210599999999999</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.6617499999999999</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.7011799999999999</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.63878</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.66038</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.58217</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.57725</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.65835</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.67465</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.62017</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.6683300000000001</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.68689</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.76036</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.67752</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.757</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.6867799999999999</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.68438</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.6860000000000001</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.6700900000000001</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.65964</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.617</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.65879</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.60148</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.5398099999999999</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.6045499999999999</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.55262</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.57766</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.55411</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.53931</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.52889</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.46604</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32928</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.9561000000000001</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.36058</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.57326</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.60448</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.6186699999999999</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.67669</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.53155</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.54547</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.4976</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.52176</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.37395</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.35204</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.36326</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.33069</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.35926</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.34579</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.32306</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.49035</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.50007</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.3572</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.38768</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.34357</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.35092</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.3553</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.37063</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.35772</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.36285</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.31632</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.31347</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.33246</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.338</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.64086</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.40807</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.5123099999999999</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.6172000000000001</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.72687</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.87026</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>1.11007</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.93177</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.5444500000000001</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>1.11289</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.8427100000000001</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.94831</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.8582799999999999</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.6391699999999999</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.8088200000000001</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>1.0663</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.33121</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.5668800000000001</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.52198</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.43199</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.37626</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.37459</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.8739600000000001</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.99134</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.53316</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>1.18893</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.78286</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.81243</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.7374700000000001</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.73897</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.33061</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.31693</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.40387</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.38528</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.35145</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.37499</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.34418</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.35002</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.32832</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.47502</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.39261</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.37607</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.36243</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.44316</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.38144</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.3439700000000001</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.37022</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.34995</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.39756</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.49946</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.4325</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.41941</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.34999</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.4232</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.41495</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.44783</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.34426</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.42044</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.35897</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.40171</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.40044</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.59675</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.35005</v>
+      </c>
+      <c r="C126" t="n">
+        <v>1.19597</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.51241</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.70359</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.79534</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.64978</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.5836399999999999</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.45044</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.45034</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.50049</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.4399</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.43746</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.41504</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.42352</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.5005500000000001</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.43408</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.41293</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.43413</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.39041</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.42803</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.45041</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.39631</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.4235</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.43412</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.40027</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.42354</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.3966</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.4025</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.79276</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.43544</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.74825</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>1.16512</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.92088</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.6425599999999999</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>1.66385</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.70017</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>1.55406</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.33185</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>1.1635</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>1.61151</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>0.90873</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.57598</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>1.57013</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>1.33258</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>1.25713</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>1.22494</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>1.33206</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>1.00431</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>1.51815</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.32549</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.60154</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.85849</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>1.50487</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.74973</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>1.07496</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>1.07287</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.90523</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.98229</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.93592</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>1.17352</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>1.15304</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.8615</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>1.15436</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>1.60675</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.9695199999999999</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>1.01479</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>1.15375</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.94935</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.9896</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>1.58375</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.92314</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.98046</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>1.08802</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.88454</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.87217</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>1.79257</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>1.09542</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>1.55361</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.95896</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.9900399999999999</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.74271</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.38609</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.36867</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.33363</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.3405</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.32942</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.33153</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.31897</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.6041299999999999</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.48748</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.49063</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.34195</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.33946</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.33243</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.33531</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.32621</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.33167</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.33109</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.31014</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.33348</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.3322</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.32831</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.32585</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.32852</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.32871</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.32228</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.33161</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.32212</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.32786</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.32872</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.5042099999999999</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0.32507</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.34995</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.37499</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.34994</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.33881</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.44332</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.33218</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.33457</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.319</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.54762</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.33716</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.39269</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.34256</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.58654</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.49663</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.47722</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.49057</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.48625</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.31487</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.5292</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>0.83304</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>0.71416</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.30854</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.54476</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.56504</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.7204299999999999</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.8475499999999999</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.56721</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.5714</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.57316</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.50795</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.50766</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.555</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.61393</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.55661</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.56711</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.45084</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.44695</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.45702</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.45939</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.37161</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.67677</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.37854</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.4027</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.36159</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.40542</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.34364</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.37994</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.3466</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.40024</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.36071</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.38491</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.54003</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.5080899999999999</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.39356</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.40188</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.39772</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.45648</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.43992</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.4392799999999999</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.4442</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.44427</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.50988</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.50324</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.50673</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.3916</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.35974</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.36038</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.34804</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.34934</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.3397</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.56755</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.4471</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.46868</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.42386</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.41593</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.37013</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.38108</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.38021</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.46779</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.56762</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.5252</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.53184</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.51891</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.54557</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.48935</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.51201</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.35027</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.43854</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.35526</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.34521</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.39795</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.4372200000000001</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.39795</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.49863</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.5194</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.52539</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.52089</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.4827</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.46993</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.45294</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.3424</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.32934</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.34858</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.35154</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.37549</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.29465</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.3169</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.31683</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.33308</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.29385</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.3202</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.5539500000000001</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.29348</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.33139</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.35664</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.32111</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.2815</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.26674</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.30018</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.30776</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.31691</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.30627</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.31836</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.46996</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.30689</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.33072</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.31393</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.33144</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.32896</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.33379</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.3643</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.31382</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.38221</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.48507</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.70104</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.60284</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.62773</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.8490800000000001</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>1.27162</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>1.16652</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.8522799999999999</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.45079</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.39647</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.42879</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.7014600000000001</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.94033</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>1.16808</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>1.12178</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>1.01866</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.5418999999999999</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.4388</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.42964</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.39711</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.37978</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.41952</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.392</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.49713</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.44596</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.41321</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.42488</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.3803</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.38036</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.38532</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.34999</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.36025</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.34019</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.36609</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.41871</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.3707</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.56311</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.38051</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.35277</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.34951</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.36025</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.35177</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.342</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.3478</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.34581</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.45948</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.4566</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.45949</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.43682</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.50013</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.40183</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.43553</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.39839</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.34194</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.3365</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.43915</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.48228</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.50499</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.50518</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.57748</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.71345</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>1.05067</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.34556</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.4136</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>1.11026</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.9907899999999999</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.97951</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>0.98105</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>1.56602</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>1.54701</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.94638</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>1.08632</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>1.784</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>1.01334</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>1.768</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>1.64857</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>1.64131</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>1.70861</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.80013</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>1.29861</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.32726</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.9296599999999999</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>1.51944</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.6523300000000001</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>1.31338</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>1.13999</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>1.62401</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>1.65765</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>1.67102</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>1.66609</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>1.64306</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>1.66756</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>1.20689</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>1.70048</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>1.78228</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>1.69779</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>1.70557</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>1.71372</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>1.63328</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>1.74802</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>1.02178</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>1.13158</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>1.69163</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>1.70007</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>1.69384</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>1.77347</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>1.72363</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.81302</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.6664500000000001</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.463</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>1.062</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.4641</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.34574</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.57737</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.45433</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.48715</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>0.34216</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.34412</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.33382</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.44869</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.5973200000000001</v>
+      </c>
+      <c r="E130" t="n">
+        <v>1.17372</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.47448</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.49787</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.34499</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.39136</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.35483</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.48804</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.34608</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.46118</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.50586</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.49836</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.49328</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.4529</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.33473</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.33953</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.33686</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.33298</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.32964</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.32819</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.33043</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.33254</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.44053</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.33829</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.34597</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.34076</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.34565</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.34034</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.33875</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.33561</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.35077</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.34606</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.39776</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.40224</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.34475</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.42534</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.74694</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.49506</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.51066</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.51889</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.33807</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.29769</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.3421</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.3415</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.30112</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.32665</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.28465</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.33819</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.33941</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.32315</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.33892</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.32849</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.33348</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.34401</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.3430299999999999</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.34131</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.32782</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.34429</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.33589</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.40651</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.45214</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.92223</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>1.47464</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>1.17952</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.90234</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.7632599999999999</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.45004</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.39444</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.35005</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.35007</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.35007</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.45569</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.50032</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.4975</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.44913</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.48988</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.36771</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.36163</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.36793</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.36254</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.37323</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.36208</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.39308</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.38554</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.37163</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.4029700000000001</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.355</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.37995</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.36957</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.36098</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.35027</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.35004</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.34937</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.34929</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.3395899999999999</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.35133</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.35546</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.35552</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.35138</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.35084</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.35004</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.34946</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.34941</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.34626</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.37091</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.34705</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.3497</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.34949</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.33705</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.3408</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.34004</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.34061</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.36933</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.32438</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.33981</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.34057</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.3495</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.33879</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.33965</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.34504</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.3359</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.34949</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.34949</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.33634</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.34011</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.33349</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.34855</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.40487</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.34527</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.40483</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.30028</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.34441</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.33678</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.43844</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.36951</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.33394</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.34997</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.33298</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.33011</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.34144</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.32569</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.33469</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.3188</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.37966</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.34094</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.44865</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.74653</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.42617</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.51503</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>1.68043</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.49589</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.40555</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.41863</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.42695</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.35409</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.33181</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.34361</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.34561</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.42188</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.5661900000000001</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.38969</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.35462</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.42538</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.45379</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.35234</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.40095</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.34722</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.36031</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.36025</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.36228</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.35022</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.66462</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.44921</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.45068</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.38357</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.43035</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.40911</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.38576</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.38517</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.65181</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.8316399999999999</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.47209</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.40275</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.45941</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.39339</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.35068</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.35095</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.3596</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.33989</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.34479</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.32533</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.5210399999999999</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.48609</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.48118</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.6971900000000001</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.4694700000000001</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.43961</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.42646</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.39708</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.40875</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.39642</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.35359</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.36064</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.36081</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.35681</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.35236</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.35978</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.36011</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.35978</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.34011</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.37086</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.35879</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.35651</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.36008</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.36008</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.37949</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.36587</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.37991</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.35653</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.35649</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.35113</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.35182</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.35817</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.34974</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.32989</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.3771600000000001</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.43923</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.51647</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.41889</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.5460900000000001</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.7615499999999999</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.34586</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.34556</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.36107</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.76825</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.33185</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.34648</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.34282</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.27724</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.33227</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.47989</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.33619</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.34218</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.34044</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.39417</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.54667</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.50163</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.3518</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.36073</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.72326</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.7626799999999999</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.5542899999999999</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.50187</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.45116</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>1.02064</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>1.48741</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>1.44705</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>1.09501</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>1.12993</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>1.08392</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.36809</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>1.11242</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>1.12888</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>1.01867</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>1.19447</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>1.14274</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>1.13195</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>1.1743</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.84137</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>1.19133</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.84846</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>1.34122</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.90391</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>1.73425</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.75782</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.94909</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>1.66411</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>1.38935</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>1.54696</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.5402100000000001</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.52916</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.53372</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.46364</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.36731</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.36016</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.3454</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.7559600000000001</v>
+      </c>
+      <c r="D133" t="n">
+        <v>1.37058</v>
+      </c>
+      <c r="E133" t="n">
+        <v>1.34712</v>
+      </c>
+      <c r="F133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.41947</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.42729</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.51518</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.61149</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.60588</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.52798</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.51029</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.5731000000000001</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.58887</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.5898600000000001</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.5151399999999999</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.58392</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.5299400000000001</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.5730299999999999</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.50356</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.46067</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.46827</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.46823</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.5016499999999999</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.42927</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.49842</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.45692</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.6368400000000001</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.5470499999999999</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.49859</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.6803400000000001</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.53673</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>1.0246</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>1.77262</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.35854</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.74054</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>1.27914</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>1.34065</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>1.717</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>1.64053</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>1.34719</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.9944400000000001</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>1.59103</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.49285</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.49439</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.53892</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.5893999999999999</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.73276</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>1.17609</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.69048</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.91151</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.66418</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.93314</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.87963</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>1.74416</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>1.71344</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>1.17509</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>1.17628</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>1.42425</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>1.23529</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>1.61464</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>1.20314</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>1.28236</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>1.07584</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>1.39751</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>1.03286</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.66412</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.63522</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.43029</v>
+      </c>
+      <c r="C134" t="n">
+        <v>1.13528</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.63219</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.47272</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.5042099999999999</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.45169</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.42656</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.44839</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.41786</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.40084</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.45773</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.39936</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.40707</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.39868</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.38858</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.37995</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.3749</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.36008</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.35688</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.36586</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.37684</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.37126</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.36021</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.35985</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.36586</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.38661</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.39026</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.3796</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.36649</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.36138</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.35512</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.37963</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.44887</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.48274</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.40502</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.5252599999999999</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.39427</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.38661</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.35164</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.3685</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.53183</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.80079</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.6678999999999999</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.64906</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>1.50875</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>1.06738</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>1.66577</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>1.66325</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>0.7957000000000001</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>1.04776</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>1.16627</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.49944</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>1.19204</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.54598</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>1.15309</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.55669</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.57174</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.42789</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>0.49751</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.23461</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.34213</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.32464</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.32099</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.35264</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.37327</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.3503500000000001</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.42977</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.47864</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.45917</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.50064</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.5113</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.46054</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.36357</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.41265</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.43135</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.53814</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.5152599999999999</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.59678</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.38445</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.38768</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.4060299999999999</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.40312</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.34406</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.36535</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.37801</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.39931</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.36008</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.37949</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.35508</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.39964</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.38194</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.37501</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.3603</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.39385</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.37904</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.36413</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.3312</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.7562000000000001</v>
+      </c>
+      <c r="D135" t="n">
+        <v>1.12715</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.68649</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.55104</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.45821</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.40267</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.37659</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.37698</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.41197</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.35616</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.35974</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.3513</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.3574</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.34746</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.36941</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.34856</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.39878</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.33608</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.33973</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.3404</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.33549</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.34049</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.3455</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.33093</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.33051</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.33761</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0.33768</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.38053</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.34271</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.3396</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.33933</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0.32953</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.41657</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.3474</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.33753</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.33957</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.3443</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.35165</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.41786</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.34392</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.34156</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.3332</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.43164</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.38127</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.34781</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.49277</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.3231</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.04337</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.36582</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.33689</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.32423</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.33951</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.32592</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.34242</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.45465</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.33102</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.32163</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.30776</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.30412</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.32485</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.44753</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.29881</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.3598</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.37587</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.36021</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.41196</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.34654</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.44495</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.58026</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.47736</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.44793</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.39912</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.46198</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.44883</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.46307</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.34279</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.5451</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.39192</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.44589</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.42312</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.39762</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.41176</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.3766</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.45959</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.41924</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.46757</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.49141</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.47539</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.48009</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.49806</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.45975</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.40575</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.38694</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.36877</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.36958</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.33151</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.85921</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.39787</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.48162</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.40412</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.42132</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.44133</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.435</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.42992</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.4296</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.32315</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.32286</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.32585</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.32305</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.3235</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.32356</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.31093</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.32695</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.32073</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.31994</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.32231</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.32252</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0.32033</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.32073</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.32117</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.32288</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0.32366</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0.32812</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.37019</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.38088</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0.23334</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.3057</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.26674</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>0.38306</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.38241</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>0.3395899999999999</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>0.32038</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.29609</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>0.30114</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>0.33675</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>0.3106</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>0.1103</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>0.69828</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>0.17208</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>0.37685</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>0.29019</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>0.25965</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>0.09709000000000001</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>0.3552</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>0.33659</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>0.3440299999999999</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>0.31682</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>0.34809</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>0.6880299999999999</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.55847</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>0.30079</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>0.3145</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>0.30081</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>0.27357</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>0.30225</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>0.31647</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>0.49148</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>0.38095</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.3692</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.34285</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.38932</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.4916</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.36378</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.39012</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.35251</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.36542</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.38133</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.39838</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.37066</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.39815</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.38112</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.38402</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.41255</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.4066</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.39378</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.39148</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.38138</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.39165</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.38103</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.427</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.8019500000000001</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.38251</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.46566</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.39167</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.38738</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.3875</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.38407</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.40025</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.36834</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.4841</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.31015</v>
+      </c>
+      <c r="C137" t="n">
+        <v>1.09283</v>
+      </c>
+      <c r="D137" t="n">
+        <v>1.36526</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.84324</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.8021900000000001</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.52154</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.7529</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.75148</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.51176</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.41556</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.42681</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.4242</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.40631</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.41306</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.39326</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.38581</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.44124</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0.55401</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.35833</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0.42447</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0.38685</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0.44181</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0.5079900000000001</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.735</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.42304</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.57029</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.7970499999999999</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.45254</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.40128</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.75275</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0.4091</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.52252</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>1.28316</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>1.28653</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>1.21623</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>1.06051</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.9531499999999999</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>1.28325</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>0.61021</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>0.5442</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.38465</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.49107</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>0.57512</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>0.74942</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.54575</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.54087</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.39527</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>0.21315</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>0.35526</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>0.75237</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.75082</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>0.5748099999999999</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.44798</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>0.31672</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.49154</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.98452</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.75903</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>0.618</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.74998</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>1.17165</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.6004700000000001</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.72627</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.62364</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>1.23544</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.87249</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.85798</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.8794999999999999</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.8980900000000001</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>1.15208</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.63839</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.9306599999999999</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.67837</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.95562</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>1.61838</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>1.63647</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>1.73498</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>1.61886</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>1.79099</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>1.24312</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>1.03365</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.99476</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>1.00728</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>1.51336</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>1.34003</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>1.0477</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.40945</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.3808</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.75373</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.38925</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.34522</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.3302</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.5567000000000001</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.80102</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.5496</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.7506900000000001</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.75248</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.55891</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.46876</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.45842</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.40698</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.428</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.419</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.35824</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.37045</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.35484</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.34816</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.38242</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.38295</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.36807</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.35999</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.35192</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.36142</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0.38273</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.42185</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.40475</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.42646</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.62718</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.59013</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.5561699999999999</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.5372</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.44781</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.47313</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.49441</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.55704</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.81138</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>1.15279</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>1.11871</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>1.03162</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>1.12143</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>1.7249</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>1.71965</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>1.04245</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>1.06083</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.66788</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.55549</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.56196</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.54947</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.47712</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.28181</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.46374</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.34752</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.54625</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.55143</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.54091</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.65695</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>1.54115</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>1.04301</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.6538099999999999</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.54652</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.49689</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.49744</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.48046</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.49744</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.48025</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.49791</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.57462</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.5549299999999999</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.55843</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.49587</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.5115299999999999</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.40242</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.39934</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.38365</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.42223</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.49831</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.5582699999999999</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.6569199999999999</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>1.1516</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>1.05454</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.65816</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.5797899999999999</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>1.15033</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.8632799999999999</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.6574099999999999</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>1.13943</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.81208</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.49224</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.5095299999999999</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.49705</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.43889</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.5327499999999999</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.39081</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.39848</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.34932</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.34515</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.34433</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.37037</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.70545</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.5785399999999999</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.58508</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.71963</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.5477300000000001</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.45108</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.38366</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.39668</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.41882</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.39504</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.35806</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.3918</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.35483</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.35371</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.37899</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.36422</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.36255</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.35282</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.34652</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.3538</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.35034</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.36153</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.34317</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.36915</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.36225</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.38721</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.35943</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.62562</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.58316</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.41586</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.62919</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>1.00381</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>1.17351</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.9239400000000001</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.9604600000000001</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>1.00946</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.95048</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.91679</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.94667</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.9306</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.91392</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.9162400000000001</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.39874</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.6684099999999999</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>1.02248</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.6674500000000001</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>1.01941</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>1.12181</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>1.10367</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.69794</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.92092</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.8418099999999999</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.9087000000000001</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>1.54148</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>1.66596</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>1.68844</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>1.73685</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>1.78692</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>1.1964</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>1.07651</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>1.01601</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.4013</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>1.32861</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>1.01167</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>1.11076</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.91511</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.7512799999999999</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.75052</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.8129999999999999</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.69128</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.42435</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.69071</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.556</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.40152</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.45852</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.6881799999999999</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.38012</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.7240700000000001</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.68444</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.31989</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.37271</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.36325</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.36871</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.34704</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.74651</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.40112</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.40116</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.39181</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.38075</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.36014</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.37556</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.37443</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.37865</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.37732</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.36917</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.36693</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.36154</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.36004</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.35979</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.3604</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.35587</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.32886</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.35619</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.35107</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.34994</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.34723</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.35016</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.36016</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.37105</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.39962</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.3757799999999999</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.36964</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.3642</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.40228</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.38604</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.36611</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.69455</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.46083</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.7325199999999999</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.5195700000000001</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.50528</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.4392</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.9934299999999999</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.89051</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>1.00684</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.8951</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>1.01465</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.99749</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.9976799999999999</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.31409</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>1.16099</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>1.06688</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>1.08763</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.42334</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.36335</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.35947</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.66504</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.35062</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.5946399999999999</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.71733</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.70447</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>1.02574</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>1.6971</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>1.75013</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>1.13437</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>1.22811</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>1.42872</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>1.1972</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>1.35919</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.98138</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>1.39711</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>1.37639</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>1.73997</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>1.65073</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>1.41823</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>1.42004</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.39832</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.80728</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.75475</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.8017300000000001</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.55622</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.3695</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.37511</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.27097</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.4229</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.38736</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.37049</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.36716</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.35496</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.34994</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.35851</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.3602</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.75386</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.35912</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.34943</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.43937</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.39907</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.36636</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.37282</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.3582</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.35932</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.3584</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.35987</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.36604</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.35812</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.35656</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.37945</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.35982</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.37251</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.49792</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.37723</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.35588</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.35009</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.35716</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.34308</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.38217</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.8110700000000001</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>1.31366</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>1.00408</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.9342</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.9604199999999999</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>1.0339</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>1.16255</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>1.06182</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.86442</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.6934900000000001</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>1.22228</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>1.20858</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>1.20922</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>1.152</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.86773</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>0.32384</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>0.70365</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>1.09738</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>0.3598</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>1.10827</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.36184</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>1.1083</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>1.13455</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>1.10601</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.52067</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>1.20131</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.63961</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.5774600000000001</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>1.15272</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.73103</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.6632400000000001</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>1.18533</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.86166</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>1.06621</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>1.03223</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>1.04941</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>1.03627</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>1.06927</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>1.1283</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>1.05074</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>1.06135</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>1.18428</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>1.16282</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>1.21643</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>1.20344</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>1.26567</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>1.16953</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>1.14276</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>1.12015</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>1.10079</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>1.12693</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>1.17665</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>1.19424</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>1.17482</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>1.07611</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.67367</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.61429</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.56548</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.5481200000000001</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.44887</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.37918</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.37558</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.35036</v>
+      </c>
+      <c r="C142" t="n">
+        <v>1.53053</v>
+      </c>
+      <c r="D142" t="n">
+        <v>1.31377</v>
+      </c>
+      <c r="E142" t="n">
+        <v>1.31096</v>
+      </c>
+      <c r="F142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G142" t="n">
+        <v>1.06786</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.47907</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.5198700000000001</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.44218</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.39878</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.43311</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.42992</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.43191</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.44013</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.43479</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.39274</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.38506</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.43692</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.43776</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.43388</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.4261</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.4324</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.4272</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.42081</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.4172</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.40352</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.41939</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.37185</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.84836</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.42905</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.37306</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.35518</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.56633</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.68351</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.6991499999999999</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.65081</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.9410599999999999</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.75205</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.9464199999999999</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>1.15817</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>1.30593</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>1.44496</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>1.4331</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>1.45955</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>1.54527</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>1.252</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>0.85123</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>1.6198</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.73338</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.70063</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>1.50287</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.84435</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.8661599999999999</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>1.2142</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.77319</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.57997</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.58051</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.62686</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.7072200000000001</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.58278</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.7349199999999999</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>1.60988</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>1.19958</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>1.17623</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>1.41119</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>1.17759</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>1.17847</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>1.1837</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>1.10321</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>1.07796</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>1.20745</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>1.10567</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>1.19198</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>1.05052</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>1.08209</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>1.20653</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>1.08204</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>1.54218</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.8073400000000001</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.8041200000000001</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.5640299999999999</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.38092</v>
+      </c>
+      <c r="C143" t="n">
+        <v>1.21327</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.8491299999999999</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.84962</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.55913</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.55457</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.56255</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.51548</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.5539400000000001</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.41962</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.5212</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.50122</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.3733</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.45973</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.45997</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.35012</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.33347</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.38113</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.3503500000000001</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.33441</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.35984</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.35033</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.36451</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.36089</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.43863</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.39907</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.3497</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.38039</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.41211</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.4952</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.49921</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.5478</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.5203099999999999</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.52047</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.55759</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>1.17566</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.88301</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>1.49398</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>1.17068</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>1.50945</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.5694400000000001</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.8441799999999999</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.7951699999999999</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.59699</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.8529099999999999</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.5009</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.5229299999999999</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.54367</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>1.17768</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.701</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.55537</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>1.1737</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.54926</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.5504</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.5807899999999999</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>0.79963</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.5551</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.79916</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.84911</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>1.17425</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.7987000000000001</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.6835599999999999</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>1.05133</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>1.1749</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>1.1759</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>1.17726</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>1.17519</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.8242200000000001</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.7324700000000001</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.64503</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.6766</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.68459</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.73111</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.83484</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.8180499999999999</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.61524</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.80662</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.7563200000000001</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>1.13661</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.75054</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.6094700000000001</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.63615</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.6382899999999999</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.6172000000000001</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.6145499999999999</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.7035</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.6705399999999999</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.81352</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.70409</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.60814</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.531</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.51249</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.40856</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.40972</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.38405</v>
       </c>
     </row>
   </sheetData>
